--- a/financial_models/opportunities/9961.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9961.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B119A7-BD7D-4418-9C85-0E2F6F448318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17325DF1-B222-4923-9E1E-5DFE7C4F86B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.1618874917917271</v>
+        <v>0.22033584470025575</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1499999999999999</v>
+        <v>1.143294</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>650.62534451664794</v>
+        <v>753.83596143870022</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,13 +5561,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>299.82734770352448</v>
+        <v>343.12060147414661</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5576,13 +5576,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>375.81247336701699</v>
+        <v>436.24766286961818</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>466.34247764114394</v>
+        <v>540.3197599894944</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>527.39872343314846</v>
+        <v>611.06153809014074</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>4.3000834340575951E-2</v>
+        <v>4.2750083388325602E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-52.291661600432249</v>
+        <v>-51.986733006786601</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>64.673688290789485</v>
+        <v>64.296556331069468</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>93.456458250173469</v>
+        <v>92.911485198846819</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>105.83848494053072</v>
+        <v>105.22130852312968</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>28.203386754513204</v>
+        <v>28.038924222708193</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>452.3809802959654</v>
+        <v>449.74300911869176</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>1309.54 HKD</v>
+        <v>1301.9 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.20797748551668271</v>
+        <v>-0.16651179664669991</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6386,11 +6386,11 @@
       </c>
       <c r="C119" s="198">
         <f>DCF!C91</f>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>802.29 HKD</v>
+        <v>965.98 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-6.7461464704084456E-2</v>
+        <v>-7.933076973604565E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6408,11 +6408,11 @@
       </c>
       <c r="C120" s="198">
         <f>DCF!C92</f>
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>515.18 HKD</v>
+        <v>663.56 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>8.0913603223846914E-2</v>
+        <v>4.343481851307502E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6430,11 +6430,11 @@
       </c>
       <c r="C121" s="198">
         <f>DCF!C93</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>407.35 HKD</v>
+        <v>472.26 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.16892600543127573</v>
+        <v>0.16868977413758415</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>353.58 HKD</v>
+        <v>351.52 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.2254037364474995</v>
+        <v>0.28955874359217809</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>650.62534451664794</v>
+        <v>753.83596143870022</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6589,15 +6589,15 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>299.82734770352448</v>
+        <v>343.12060147414661</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>299.82734770352448</v>
+        <v>343.12060147414661</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6610,15 +6610,15 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>375.81247336701699</v>
+        <v>436.24766286961818</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>375.81247336701699</v>
+        <v>436.24766286961818</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>466.34247764114394</v>
+        <v>540.3197599894944</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>466.34247764114394</v>
+        <v>540.3197599894944</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>527.39872343314846</v>
+        <v>611.06153809014074</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>527.39872343314846</v>
+        <v>611.06153809014074</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -10004,11 +10004,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>284.92366989673479</v>
+        <v>283.26219326166739</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>28.203386754513204</v>
+        <v>28.038924222708193</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10414,11 +10414,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-36052.5</v>
+        <v>-35842.266900000002</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-52.291661600432249</v>
+        <v>-51.986733006786601</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10431,11 +10431,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>44589.291595285897</v>
+        <v>44329.277865339827</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>64.673688290789485</v>
+        <v>64.296556331069468</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10448,11 +10448,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>64433.579999999994</v>
+        <v>64057.848184800001</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>93.456458250173469</v>
+        <v>92.911485198846819</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10465,11 +10465,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>72970.371595285891</v>
+        <v>72544.859150139819</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>105.83848494053071</v>
+        <v>105.22130852312969</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15217,18 +15217,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>17.836746084470903</v>
+        <v>17.73273458947746</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>15.757953987639805</v>
+        <v>15.666064562038839</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>16.788266606165074</v>
+        <v>16.690369114112084</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15274,18 +15274,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.3000834340575951E-2</v>
+        <v>4.2750083388325602E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.7989281551687092E-2</v>
+        <v>3.7767754489003949E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>4.0473159609848298E-2</v>
+        <v>4.0237148298245137E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>105.83848494053072</v>
+        <v>105.22130852312968</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1499999999999999</v>
+        <v>1.143294</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>311894.18719839409</v>
+        <v>310075.43726852245</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>452.3809802959654</v>
+        <v>449.74300911869176</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16402,14 +16402,14 @@
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E16" s="308" t="s">
         <v>399</v>
       </c>
       <c r="F16" s="311">
         <f>Scenarios!C41</f>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
@@ -16451,7 +16451,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>650.63012580428881</v>
+        <v>753.83837835867121</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16510,11 +16510,11 @@
       </c>
       <c r="C21" s="277">
         <f>I4*(1+D21)</f>
-        <v>67223.859051512132</v>
+        <v>68272.819804071711</v>
       </c>
       <c r="D21" s="299">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E21" s="299">
         <f>$C$17</f>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="F21" s="277">
         <f>C21*E21</f>
-        <v>15627.130055199526</v>
+        <v>15870.975712594582</v>
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16530,15 +16530,15 @@
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>11518.527121685571</v>
+        <v>11698.262159935644</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
-        <v>7.7150075333880519E-2</v>
+        <v>9.3957919596079353E-2</v>
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>0.17134581805039165</v>
+        <v>0.17134581805039162</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16546,7 +16546,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>10739.885428145053</v>
+        <v>10907.470545394539</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16559,11 +16559,11 @@
       </c>
       <c r="C22" s="277">
         <f t="shared" ref="C22:C50" si="5">IF(A22="",0,C21*(1+D22))</f>
-        <v>72410.184841570444</v>
+        <v>74687.591917820289</v>
       </c>
       <c r="D22" s="299">
         <f t="shared" si="1"/>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E22" s="299">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
@@ -16571,7 +16571,7 @@
       </c>
       <c r="F22" s="277">
         <f t="shared" ref="F22:F50" si="7">IF(A22="", 0,C22*E22)</f>
-        <v>16832.764316210516</v>
+        <v>17362.179572509871</v>
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
@@ -16579,11 +16579,11 @@
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>12407.182356858955</v>
+        <v>12797.406535372735</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
-        <v>7.7150075333880297E-2</v>
+        <v>9.3957919596079353E-2</v>
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
@@ -16595,7 +16595,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>10786.450720749361</v>
+        <v>11125.700499669299</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16608,11 +16608,11 @@
       </c>
       <c r="C23" s="277">
         <f t="shared" si="5"/>
-        <v>77996.636057037802</v>
+        <v>81705.082674059639</v>
       </c>
       <c r="D23" s="299">
         <f t="shared" si="1"/>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
@@ -16620,7 +16620,7 @@
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>18131.413351283609</v>
+        <v>18993.493844796445</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
@@ -16628,15 +16628,15 @@
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>13364.397410371812</v>
+        <v>13999.824229661628</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
-        <v>7.7150075333880075E-2</v>
+        <v>9.3957919596079575E-2</v>
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>0.17134581805039159</v>
+        <v>0.17134581805039162</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>10833.217908102899</v>
+        <v>11348.296664491645</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -16665,11 +16665,11 @@
       </c>
       <c r="C24" s="277">
         <f t="shared" si="5"/>
-        <v>84014.082404627508</v>
+        <v>89381.922262539956</v>
       </c>
       <c r="D24" s="299">
         <f t="shared" si="1"/>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E24" s="299">
         <f t="shared" si="6"/>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="F24" s="277">
         <f t="shared" si="7"/>
-        <v>19530.253257244862</v>
+        <v>20778.083012314459</v>
       </c>
       <c r="G24" s="299">
         <f t="shared" si="2"/>
@@ -16685,11 +16685,11 @@
       </c>
       <c r="H24" s="277">
         <f t="shared" si="8"/>
-        <v>14395.461677373913</v>
+        <v>15315.21858899142</v>
       </c>
       <c r="I24" s="299">
         <f t="shared" si="9"/>
-        <v>7.7150075333880297E-2</v>
+        <v>9.3957919596079353E-2</v>
       </c>
       <c r="J24" s="299">
         <f t="shared" si="10"/>
@@ -16701,7 +16701,7 @@
       </c>
       <c r="L24" s="277">
         <f t="shared" si="4"/>
-        <v>10880.187865567717</v>
+        <v>11575.346396313666</v>
       </c>
       <c r="N24" s="275"/>
       <c r="O24" s="275"/>
@@ -16722,11 +16722,11 @@
       </c>
       <c r="C25" s="277">
         <f t="shared" si="5"/>
-        <v>90495.775191251349</v>
+        <v>97780.061727826702</v>
       </c>
       <c r="D25" s="299">
         <f t="shared" si="1"/>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E25" s="299">
         <f t="shared" si="6"/>
@@ -16734,7 +16734,7 @@
       </c>
       <c r="F25" s="277">
         <f t="shared" si="7"/>
-        <v>21037.013767331064</v>
+        <v>22730.348465346164</v>
       </c>
       <c r="G25" s="299">
         <f t="shared" si="2"/>
@@ -16742,15 +16742,15 @@
       </c>
       <c r="H25" s="277">
         <f t="shared" si="8"/>
-        <v>15506.072630249297</v>
+        <v>16754.204665772257</v>
       </c>
       <c r="I25" s="299">
         <f t="shared" si="9"/>
-        <v>7.7150075333880297E-2</v>
+        <v>9.3957919596079353E-2</v>
       </c>
       <c r="J25" s="299">
         <f t="shared" si="10"/>
-        <v>0.17134581805039162</v>
+        <v>0.17134581805039165</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="L25" s="277">
         <f t="shared" si="4"/>
-        <v>10927.361472301202</v>
+        <v>11806.93879936156</v>
       </c>
       <c r="N25" s="275"/>
       <c r="O25" s="275"/>
@@ -16779,11 +16779,11 @@
       </c>
       <c r="C26" s="277">
         <f t="shared" si="5"/>
-        <v>97477.531064654293</v>
+        <v>106967.27290574952</v>
       </c>
       <c r="D26" s="299">
         <f t="shared" si="1"/>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E26" s="299">
         <f t="shared" si="6"/>
@@ -16791,7 +16791,7 @@
       </c>
       <c r="F26" s="277">
         <f t="shared" si="7"/>
-        <v>22660.020964280531</v>
+        <v>24866.044718844023</v>
       </c>
       <c r="G26" s="299">
         <f t="shared" si="2"/>
@@ -16799,15 +16799,15 @@
       </c>
       <c r="H26" s="277">
         <f t="shared" si="8"/>
-        <v>16702.367301805651</v>
+        <v>18328.394880655138</v>
       </c>
       <c r="I26" s="299">
         <f t="shared" si="9"/>
-        <v>7.7150075333880297E-2</v>
+        <v>9.3957919596078909E-2</v>
       </c>
       <c r="J26" s="299">
         <f t="shared" si="10"/>
-        <v>0.17134581805039162</v>
+        <v>0.17134581805039159</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="L26" s="277">
         <f t="shared" si="4"/>
-        <v>10974.739611272522</v>
+        <v>12043.164760604008</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -16828,11 +16828,11 @@
       </c>
       <c r="C27" s="277">
         <f t="shared" si="5"/>
-        <v>104997.92992965302</v>
+        <v>117017.69533283981</v>
       </c>
       <c r="D27" s="299">
         <f t="shared" si="1"/>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E27" s="299">
         <f t="shared" si="6"/>
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F27" s="277">
         <f t="shared" si="7"/>
-        <v>24408.24328874208</v>
+        <v>27202.406549209682</v>
       </c>
       <c r="G27" s="299">
         <f t="shared" si="2"/>
@@ -16848,15 +16848,15 @@
       </c>
       <c r="H27" s="277">
         <f t="shared" si="8"/>
-        <v>17990.956197394091</v>
+        <v>20050.492733176929</v>
       </c>
       <c r="I27" s="299">
         <f t="shared" si="9"/>
-        <v>7.7150075333880075E-2</v>
+        <v>9.3957919596079575E-2</v>
       </c>
       <c r="J27" s="299">
         <f t="shared" si="10"/>
-        <v>0.17134581805039156</v>
+        <v>0.17134581805039159</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="L27" s="277">
         <f t="shared" si="4"/>
-        <v>11022.323169279176</v>
+        <v>12284.116985420214</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -16877,11 +16877,11 @@
       </c>
       <c r="C28" s="277">
         <f t="shared" si="5"/>
-        <v>113098.52813362723</v>
+        <v>128012.43454224129</v>
       </c>
       <c r="D28" s="299">
         <f t="shared" si="1"/>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E28" s="299">
         <f t="shared" si="6"/>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="F28" s="277">
         <f t="shared" si="7"/>
-        <v>26291.341097236211</v>
+        <v>29758.288076580189</v>
       </c>
       <c r="G28" s="299">
         <f t="shared" si="2"/>
@@ -16897,11 +16897,11 @@
       </c>
       <c r="H28" s="277">
         <f t="shared" si="8"/>
-        <v>19378.95982335159</v>
+        <v>21934.395317262544</v>
       </c>
       <c r="I28" s="299">
         <f t="shared" si="9"/>
-        <v>7.7150075333880519E-2</v>
+        <v>9.3957919596079575E-2</v>
       </c>
       <c r="J28" s="299">
         <f t="shared" si="10"/>
@@ -16913,7 +16913,7 @@
       </c>
       <c r="L28" s="277">
         <f t="shared" si="4"/>
-        <v>11070.113036963581</v>
+        <v>12529.890033981503</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -16926,11 +16926,11 @@
       </c>
       <c r="C29" s="277">
         <f t="shared" si="5"/>
-        <v>121824.08809928755</v>
+        <v>140040.21657425957</v>
       </c>
       <c r="D29" s="299">
         <f t="shared" si="1"/>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E29" s="299">
         <f t="shared" si="6"/>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="F29" s="277">
         <f t="shared" si="7"/>
-        <v>28319.720043516725</v>
+        <v>32554.314914996481</v>
       </c>
       <c r="G29" s="299">
         <f t="shared" si="2"/>
@@ -16946,15 +16946,15 @@
       </c>
       <c r="H29" s="277">
         <f t="shared" si="8"/>
-        <v>20874.048033615403</v>
+        <v>23995.30546887052</v>
       </c>
       <c r="I29" s="299">
         <f t="shared" si="9"/>
-        <v>7.7150075333880297E-2</v>
+        <v>9.3957919596079353E-2</v>
       </c>
       <c r="J29" s="299">
         <f t="shared" si="10"/>
-        <v>0.17134581805039162</v>
+        <v>0.17134581805039165</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
@@ -16962,7 +16962,7 @@
       </c>
       <c r="L29" s="277">
         <f t="shared" si="4"/>
-        <v>11118.110108829735</v>
+        <v>12780.580358360887</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -16975,11 +16975,11 @@
       </c>
       <c r="C30" s="277">
         <f t="shared" si="5"/>
-        <v>131222.82567362886</v>
+        <v>153198.10398336139</v>
       </c>
       <c r="D30" s="299">
         <f t="shared" si="1"/>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E30" s="299">
         <f t="shared" si="6"/>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="F30" s="277">
         <f t="shared" si="7"/>
-        <v>30504.588578308441</v>
+        <v>35613.050618285168</v>
       </c>
       <c r="G30" s="299">
         <f t="shared" si="2"/>
@@ -16995,11 +16995,11 @@
       </c>
       <c r="H30" s="277">
         <f t="shared" si="8"/>
-        <v>22484.482411931869</v>
+        <v>26249.854450798015</v>
       </c>
       <c r="I30" s="299">
         <f t="shared" si="9"/>
-        <v>7.7150075333880297E-2</v>
+        <v>9.3957919596079131E-2</v>
       </c>
       <c r="J30" s="299">
         <f t="shared" si="10"/>
@@ -17011,7 +17011,7 @@
       </c>
       <c r="L30" s="277">
         <f t="shared" si="4"/>
-        <v>11166.315283259977</v>
+        <v>13036.286340385072</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -17024,11 +17024,11 @@
       </c>
       <c r="C31" s="277">
         <f t="shared" si="5"/>
-        <v>141346.67655987397</v>
+        <v>167592.27911970185</v>
       </c>
       <c r="D31" s="299">
         <f t="shared" si="1"/>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E31" s="299">
         <f t="shared" si="6"/>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="F31" s="277">
         <f t="shared" si="7"/>
-        <v>32858.019885153961</v>
+        <v>38959.178764849108</v>
       </c>
       <c r="G31" s="299">
         <f t="shared" si="2"/>
@@ -17044,15 +17044,15 @@
       </c>
       <c r="H31" s="277">
         <f t="shared" si="8"/>
-        <v>24219.161923855718</v>
+        <v>28716.236164694878</v>
       </c>
       <c r="I31" s="299">
         <f t="shared" si="9"/>
-        <v>7.7150075333880297E-2</v>
+        <v>9.3957919596079131E-2</v>
       </c>
       <c r="J31" s="299">
         <f t="shared" si="10"/>
-        <v>0.17134581805039162</v>
+        <v>0.17134581805039159</v>
       </c>
       <c r="K31" s="119">
         <f t="shared" si="3"/>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="L31" s="277">
         <f t="shared" si="4"/>
-        <v>11214.729462531788</v>
+        <v>13297.108330243766</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -17073,11 +17073,11 @@
       </c>
       <c r="C32" s="277">
         <f t="shared" si="5"/>
-        <v>152251.58330466185</v>
+        <v>183338.90100615448</v>
       </c>
       <c r="D32" s="299">
         <f t="shared" si="1"/>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E32" s="299">
         <f t="shared" si="6"/>
@@ -17085,7 +17085,7 @@
       </c>
       <c r="F32" s="277">
         <f t="shared" si="7"/>
-        <v>35393.018594615729</v>
+        <v>42619.702150766076</v>
       </c>
       <c r="G32" s="299">
         <f t="shared" si="2"/>
@@ -17093,11 +17093,11 @@
       </c>
       <c r="H32" s="277">
         <f t="shared" si="8"/>
-        <v>26087.672090804634</v>
+        <v>31414.353973359306</v>
       </c>
       <c r="I32" s="299">
         <f t="shared" si="9"/>
-        <v>7.7150075333880297E-2</v>
+        <v>9.3957919596079353E-2</v>
       </c>
       <c r="J32" s="299">
         <f t="shared" si="10"/>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="L32" s="277">
         <f t="shared" si="4"/>
-        <v>11263.353552834687</v>
+        <v>13563.148685871483</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -17122,11 +17122,11 @@
       </c>
       <c r="C33" s="277">
         <f t="shared" si="5"/>
-        <v>163997.80442631905</v>
+        <v>200565.04272572428</v>
       </c>
       <c r="D33" s="299">
         <f t="shared" si="1"/>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E33" s="299">
         <f t="shared" si="6"/>
@@ -17134,7 +17134,7 @@
       </c>
       <c r="F33" s="277">
         <f t="shared" si="7"/>
-        <v>38123.592645483754</v>
+        <v>46624.160698656604</v>
       </c>
       <c r="G33" s="299">
         <f t="shared" si="2"/>
@@ -17142,11 +17142,11 @@
       </c>
       <c r="H33" s="277">
         <f t="shared" si="8"/>
-        <v>28100.337957895772</v>
+        <v>34365.981318150974</v>
       </c>
       <c r="I33" s="299">
         <f t="shared" si="9"/>
-        <v>7.7150075333880075E-2</v>
+        <v>9.3957919596079353E-2</v>
       </c>
       <c r="J33" s="299">
         <f t="shared" si="10"/>
@@ -17158,7 +17158,7 @@
       </c>
       <c r="L33" s="277">
         <f t="shared" si="4"/>
-        <v>11312.188464287186</v>
+        <v>13834.51181311726</v>
       </c>
       <c r="N33" s="275"/>
       <c r="O33" s="275"/>
@@ -17179,11 +17179,11 @@
       </c>
       <c r="C34" s="277">
         <f t="shared" si="5"/>
-        <v>176650.24739240055</v>
+        <v>219409.71688393209</v>
       </c>
       <c r="D34" s="299">
         <f t="shared" si="1"/>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E34" s="299">
         <f t="shared" si="6"/>
@@ -17191,7 +17191,7 @@
       </c>
       <c r="F34" s="277">
         <f t="shared" si="7"/>
-        <v>41064.830690080991</v>
+        <v>51004.869840815663</v>
       </c>
       <c r="G34" s="299">
         <f t="shared" si="2"/>
@@ -17199,15 +17199,15 @@
       </c>
       <c r="H34" s="277">
         <f t="shared" si="8"/>
-        <v>30268.281148254926</v>
+        <v>37594.937427682169</v>
       </c>
       <c r="I34" s="299">
         <f t="shared" si="9"/>
-        <v>7.7150075333880297E-2</v>
+        <v>9.3957919596079353E-2</v>
       </c>
       <c r="J34" s="299">
         <f t="shared" si="10"/>
-        <v>0.17134581805039159</v>
+        <v>0.17134581805039162</v>
       </c>
       <c r="K34" s="119">
         <f t="shared" si="3"/>
@@ -17215,7 +17215,7 @@
       </c>
       <c r="L34" s="277">
         <f t="shared" si="4"/>
-        <v>11361.235110953841</v>
+        <v>14111.304206718083</v>
       </c>
       <c r="N34" s="275"/>
       <c r="O34" s="275"/>
@@ -17236,11 +17236,11 @@
       </c>
       <c r="C35" s="277">
         <f t="shared" si="5"/>
-        <v>190278.82728647284</v>
+        <v>240024.99742151113</v>
       </c>
       <c r="D35" s="299">
         <f t="shared" si="1"/>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E35" s="299">
         <f t="shared" si="6"/>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="F35" s="277">
         <f t="shared" si="7"/>
-        <v>44232.985471393782</v>
+        <v>55797.181300327517</v>
       </c>
       <c r="G35" s="299">
         <f t="shared" si="2"/>
@@ -17256,11 +17256,11 @@
       </c>
       <c r="H35" s="277">
         <f t="shared" si="8"/>
-        <v>32603.481319069862</v>
+        <v>41127.279535731956</v>
       </c>
       <c r="I35" s="299">
         <f t="shared" si="9"/>
-        <v>7.7150075333880297E-2</v>
+        <v>9.3957919596079131E-2</v>
       </c>
       <c r="J35" s="299">
         <f t="shared" si="10"/>
@@ -17272,7 +17272,7 @@
       </c>
       <c r="L35" s="277">
         <f t="shared" si="4"/>
-        <v>11410.494410862339</v>
+        <v>14393.634492092042</v>
       </c>
       <c r="N35" s="275"/>
       <c r="O35" s="275"/>
@@ -18060,7 +18060,7 @@
       </c>
       <c r="C51" s="277">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>194084.40383220228</v>
+        <v>244825.49736994135</v>
       </c>
       <c r="D51" s="301">
         <f>Terminal_Growth</f>
@@ -18072,7 +18072,7 @@
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>45117.645180821652</v>
+        <v>56913.124926334065</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
@@ -18080,11 +18080,11 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>458697.25442001736</v>
+        <v>578618.27760616003</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
-        <v>2.0000000000000018E-2</v>
+        <v>2.000000000000024E-2</v>
       </c>
       <c r="J51" s="454"/>
       <c r="K51" s="119">
@@ -18093,7 +18093,7 @@
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>160533.85240109771</v>
+        <v>202503.54733701912</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18106,7 +18106,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>326614.55800703872</v>
+        <v>391141.04624904413</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18130,7 +18130,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>326614.55800703872</v>
+        <v>391141.04624904413</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18138,15 +18138,15 @@
       </c>
       <c r="C55" s="123">
         <f>C93</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D55" s="123">
         <f>C92</f>
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="E55" s="123">
         <f>C91</f>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="F55" s="123">
         <f>C90</f>
@@ -18168,13 +18168,13 @@
         <v>150247.36745775776</v>
       </c>
       <c r="C56" s="118">
-        <v>153252.31480691294</v>
+        <v>156257.26215606809</v>
       </c>
       <c r="D56" s="118">
-        <v>157759.73583064566</v>
+        <v>162267.15685437841</v>
       </c>
       <c r="E56" s="118">
-        <v>165272.10420353358</v>
+        <v>168277.0515526887</v>
       </c>
       <c r="F56" s="118">
         <v>172784.47257642139</v>
@@ -18194,13 +18194,13 @@
         <v>150061.43460742629</v>
       </c>
       <c r="C57" s="118">
-        <v>155920.51532394614</v>
+        <v>161891.66866887273</v>
       </c>
       <c r="D57" s="118">
-        <v>164919.2725769885</v>
+        <v>174170.19324394604</v>
       </c>
       <c r="E57" s="118">
-        <v>180477.56447409283</v>
+        <v>186897.00833264628</v>
       </c>
       <c r="F57" s="118">
         <v>196736.31029873894</v>
@@ -18220,13 +18220,13 @@
         <v>149888.07064441321</v>
       </c>
       <c r="C58" s="118">
-        <v>158458.10462685884</v>
+        <v>167355.33559038021</v>
       </c>
       <c r="D58" s="118">
-        <v>171928.60925172982</v>
+        <v>186156.46765022393</v>
       </c>
       <c r="E58" s="118">
-        <v>196072.90834133301</v>
+        <v>206341.62520309145</v>
       </c>
       <c r="F58" s="118">
         <v>222418.93349749438</v>
@@ -18246,13 +18246,13 @@
         <v>149726.4259236551</v>
       </c>
       <c r="C59" s="118">
-        <v>160871.47627158699</v>
+        <v>172653.4368475996</v>
       </c>
       <c r="D59" s="118">
-        <v>178790.89690532262</v>
+        <v>198226.562157245</v>
       </c>
       <c r="E59" s="118">
-        <v>212068.13282055379</v>
+        <v>226647.42557129517</v>
       </c>
       <c r="F59" s="118">
         <v>249957.41058706888</v>
@@ -18272,13 +18272,13 @@
         <v>149575.70823530253</v>
       </c>
       <c r="C60" s="118">
-        <v>163166.71084279698</v>
+        <v>177790.98958187297</v>
       </c>
       <c r="D60" s="118">
-        <v>185509.22048226668</v>
+        <v>210381.06291956</v>
       </c>
       <c r="E60" s="118">
-        <v>228473.49126078017</v>
+        <v>247852.55043133095</v>
       </c>
       <c r="F60" s="118">
         <v>279485.84755957313</v>
@@ -18298,13 +18298,13 @@
         <v>149435.17892215331</v>
       </c>
       <c r="C61" s="118">
-        <v>165349.59127415752</v>
+        <v>182772.85889995619</v>
       </c>
       <c r="D61" s="118">
-        <v>192086.60020794615</v>
+        <v>222620.56019070232</v>
       </c>
       <c r="E61" s="118">
-        <v>245299.49991742265</v>
+        <v>269996.83000544744</v>
       </c>
       <c r="F61" s="118">
         <v>311148.0410499039</v>
@@ -18324,13 +18324,13 @@
         <v>149304.14925954334</v>
       </c>
       <c r="C62" s="118">
-        <v>167425.61741866823</v>
+        <v>187603.76248112789</v>
       </c>
       <c r="D62" s="118">
-        <v>198525.99294637365</v>
+        <v>234945.64835185267</v>
       </c>
       <c r="E62" s="118">
-        <v>262556.9446934663</v>
+        <v>293121.85855837096</v>
       </c>
       <c r="F62" s="118">
         <v>345098.17859198363</v>
@@ -18350,13 +18350,13 @@
         <v>149181.97707995359</v>
       </c>
       <c r="C63" s="118">
-        <v>169400.01990575541</v>
+        <v>192288.27504468829</v>
       </c>
       <c r="D63" s="118">
-        <v>204830.2935294495</v>
+        <v>247356.92594070337</v>
       </c>
       <c r="E63" s="118">
-        <v>280256.88805351092</v>
+        <v>317271.07252506044</v>
       </c>
       <c r="F63" s="118">
         <v>381501.58947626484</v>
@@ -18376,13 +18376,13 @@
         <v>149068.06362579064</v>
       </c>
       <c r="C64" s="118">
-        <v>171277.77332004806</v>
+        <v>196830.83268208016</v>
       </c>
       <c r="D64" s="118">
-        <v>211002.33605833491</v>
+        <v>259854.99568052503</v>
       </c>
       <c r="E64" s="118">
-        <v>298410.67611509521</v>
+        <v>342489.83209866611</v>
       </c>
       <c r="F64" s="118">
         <v>420535.54986500466</v>
@@ -18402,13 +18402,13 @@
         <v>148961.85061491613</v>
       </c>
       <c r="C65" s="118">
-        <v>173063.60873503971</v>
+        <v>201235.73705773288</v>
       </c>
       <c r="D65" s="118">
-        <v>217044.89517752346</v>
+        <v>272440.46450943634</v>
       </c>
       <c r="E65" s="118">
-        <v>317029.9459218483</v>
+        <v>368825.50643194199</v>
       </c>
       <c r="F65" s="118">
         <v>462390.14608603093</v>
@@ -18428,13 +18428,13 @@
         <v>148529.25596181204</v>
       </c>
       <c r="C66" s="277">
-        <v>180764.01155060268</v>
+        <v>221337.11140539599</v>
       </c>
       <c r="D66" s="118">
-        <v>245408.54520526822</v>
+        <v>336700.33659500268</v>
       </c>
       <c r="E66" s="118">
-        <v>417537.13864620135</v>
+        <v>519067.69521386863</v>
       </c>
       <c r="F66" s="118">
         <v>721644.82892086473</v>
@@ -18463,13 +18463,13 @@
         <v>148224.40003483597</v>
       </c>
       <c r="C67" s="277">
-        <v>186755.40442618314</v>
+        <v>238571.89932882899</v>
       </c>
       <c r="D67" s="118">
-        <v>270919.22955467866</v>
+        <v>403238.70233275683</v>
       </c>
       <c r="E67" s="118">
-        <v>531607.82754169102</v>
+        <v>705660.7655681225</v>
       </c>
       <c r="F67" s="118">
         <v>1089121.1053850162</v>
@@ -18498,13 +18498,13 @@
         <v>148009.56350011332</v>
       </c>
       <c r="C68" s="277">
-        <v>191417.08115262742</v>
+        <v>253348.89465403894</v>
       </c>
       <c r="D68" s="118">
-        <v>293863.91457718669</v>
+        <v>472136.35138434247</v>
       </c>
       <c r="E68" s="118">
-        <v>661072.41323336493</v>
+        <v>937399.76102940191</v>
       </c>
       <c r="F68" s="118">
         <v>1609994.2957450449</v>
@@ -18533,13 +18533,13 @@
         <v>147858.16497849204</v>
       </c>
       <c r="C69" s="277">
-        <v>195044.15591690206</v>
+        <v>266018.59455469094</v>
       </c>
       <c r="D69" s="118">
-        <v>314500.70203343034</v>
+        <v>543476.93800987268</v>
       </c>
       <c r="E69" s="118">
-        <v>808008.30983054545</v>
+        <v>1225207.6732709748</v>
       </c>
       <c r="F69" s="118">
         <v>2348297.4130139016</v>
@@ -18612,15 +18612,15 @@
       </c>
       <c r="C72" s="124">
         <f>C55</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D72" s="124">
         <f>D55</f>
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="E72" s="124">
         <f>E55</f>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="F72" s="124">
         <f>F55</f>
@@ -18639,23 +18639,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>452.3809802959654</v>
+        <v>449.74300911869176</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>452.3809802959654</v>
+        <v>449.74300911869176</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>452.3809802959654</v>
+        <v>449.74300911869176</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>452.3809802959654</v>
+        <v>449.74300911869176</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>452.3809802959654</v>
+        <v>449.74300911869176</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18670,23 +18670,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>356.4504305691388</v>
+        <v>354.37185962357654</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>361.46266948171103</v>
+        <v>364.33788166759444</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>368.98102785056926</v>
+        <v>374.30390371161235</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>381.51162513199978</v>
+        <v>384.2699257556302</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>394.04222241343001</v>
+        <v>391.74444228864354</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18701,23 +18701,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>356.14029539561614</v>
+        <v>354.06353294263965</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>365.91321616492627</v>
+        <v>373.68124329543735</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>380.92310353655392</v>
+        <v>394.04233990792875</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>406.87426573636662</v>
+        <v>415.14682278011378</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>433.9937819950535</v>
+        <v>431.46303216717632</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18732,23 +18732,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>355.85112507065315</v>
+        <v>353.7760488578499</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>370.14590391959257</v>
+        <v>382.74147275273947</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>392.61464616618946</v>
+        <v>413.91880712659685</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>432.88723045879402</v>
+        <v>447.39122806442299</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>476.83228411054722</v>
+        <v>474.0517299390296</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18763,23 +18763,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>355.58150239003498</v>
+        <v>353.50799842914148</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>374.17139716878563</v>
+        <v>391.52714980224459</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>404.06091167772041</v>
+        <v>433.9342706195215</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>459.56719427666837</v>
+        <v>481.0637072424426</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>522.76634232296476</v>
+        <v>519.71793267807971</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18794,23 +18794,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>355.33010595123011</v>
+        <v>353.25806795948324</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>377.99983830088536</v>
+        <v>400.04659421388601</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>415.2670457449538</v>
+        <v>454.08970238862054</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>486.93125973089849</v>
+        <v>516.22750834209978</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>572.01964483511415</v>
+        <v>568.68402419314532</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18825,23 +18825,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>355.09570367728622</v>
+        <v>353.02503255653852</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>381.64087322372143</v>
+        <v>408.30787364335629</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>426.23808609049684</v>
+        <v>474.38608123302777</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>514.99696788908318</v>
+        <v>552.9486805860306</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>624.83204379919016</v>
+        <v>621.18845798552297</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18857,23 +18857,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>354.87714677850414</v>
+        <v>352.80775012955058</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>385.10367566781724</v>
+        <v>416.31881127193367</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>436.97896475046912</v>
+        <v>494.82439279662685</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>543.78230958978565</v>
+        <v>591.29619845381865</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>681.46072334109022</v>
+        <v>677.48691846219867</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18888,23 +18888,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>354.67336412229696</v>
+        <v>352.60515579203252</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>388.39697029996444</v>
+        <v>424.08699321479656</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>447.49451029170064</v>
+        <v>515.40562961591536</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>573.30573697512125</v>
+        <v>631.34209123882806</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>742.18145198741627</v>
+        <v>737.85356605956633</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18920,23 +18920,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>354.48335698364218</v>
+        <v>352.41625664283151</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>391.52905470536314</v>
+        <v>431.61977570484538</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>457.7894499824169</v>
+        <v>536.13079116820586</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>603.5861753190552</v>
+        <v>673.16157834298701</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>807.28992559419987</v>
+        <v>802.58237234112619</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18952,23 +18952,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>354.30619415039786</v>
+        <v>352.24012689998693</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>394.50782029371425</v>
+        <v>438.92429205883207</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>467.86841191738387</v>
+        <v>557.00088392016266</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>634.64303515898757</v>
+        <v>716.83321056364719</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>877.10320731709089</v>
+        <v>871.9885515707706</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18984,23 +18984,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>353.58462817877819</v>
+        <v>351.52276859915486</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>407.35205819541881</v>
+        <v>472.25777790512984</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>515.17885494781183</v>
+        <v>663.5610374500701</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>802.28858891819971</v>
+        <v>965.97517402652591</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>1309.5388737645078</v>
+        <v>1301.9025540362777</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19016,23 +19016,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>353.0761298384171</v>
+        <v>351.01723546737679</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>417.34567506192889</v>
+        <v>500.83769236140097</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>557.73056382164964</v>
+        <v>773.89954635968877</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>992.55799441265356</v>
+        <v>1275.3966773574077</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1922.4876806241662</v>
+        <v>1911.2770698535005</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19048,23 +19048,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>352.71778344692984</v>
+        <v>350.66097870276019</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>425.12133126192367</v>
+        <v>525.34192555483708</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>596.00219714622688</v>
+        <v>888.15038164007353</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1208.5043518043337</v>
+        <v>1659.6822685633556</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>2791.3018626670423</v>
+        <v>2775.0249319791769</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19080,23 +19080,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>352.46525138123849</v>
+        <v>350.40991922840152</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>431.17127595643461</v>
+        <v>546.35169608151352</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>630.42426751885648</v>
+        <v>1006.4522645571062</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>1453.5927786565148</v>
+        <v>2136.9452060735093</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>4022.7882029148027</v>
+        <v>3999.3301005767626</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>1309.5388737645078</v>
+        <v>1301.9025540362777</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19163,7 +19163,7 @@
       </c>
       <c r="C91" s="130">
         <f>Scenarios!C22</f>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="D91" s="133">
         <f>Scenarios!D22</f>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>802.28858891819971</v>
+        <v>965.97517402652591</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="C92" s="130">
         <f>Scenarios!C23</f>
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="D92" s="133">
         <f>Scenarios!D23</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>515.17885494781183</v>
+        <v>663.5610374500701</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="C93" s="130">
         <f>Scenarios!C24</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D93" s="133">
         <f>Scenarios!D24</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>407.35205819541881</v>
+        <v>472.25777790512984</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>353.58462817877819</v>
+        <v>351.52276859915486</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19607,7 +19607,7 @@
         <v>444</v>
       </c>
       <c r="C22" s="324">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="D22" s="325">
         <f>C18</f>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>802.28858891819971</v>
+        <v>965.97517402652591</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19631,7 +19631,7 @@
         <v>436</v>
       </c>
       <c r="C23" s="324">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="D23" s="325">
         <f>C18</f>
@@ -19639,7 +19639,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>515.17885494781183</v>
+        <v>663.5610374500701</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19654,7 +19654,7 @@
         <v>445</v>
       </c>
       <c r="C24" s="324">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D24" s="325">
         <f>C18</f>
@@ -19662,7 +19662,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>407.35205819541881</v>
+        <v>472.25777790512984</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>545.64410255379107</v>
+        <v>676.21804987912617</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>1309.5388737645078</v>
+        <v>1301.9025540362777</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>353.58462817877819</v>
+        <v>351.52276859915486</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19804,7 +19804,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1618874917917271</v>
+        <v>0.22033584470025575</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19813,7 +19813,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>452.3809802959654</v>
+        <v>449.74300911869176</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.12877889263249745</v>
+        <v>0.18787518536183473</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>650.62534451664794</v>
+        <v>753.83596143870022</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="C41" s="455">
         <f>DCF!C16</f>
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="E41" s="97"/>
     </row>
@@ -19923,7 +19923,7 @@
         <v>111</v>
       </c>
       <c r="C46" s="138">
-        <v>7.7150075333880214E-2</v>
+        <v>9.3957919596079284E-2</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="221" t="s">
@@ -19936,7 +19936,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>650.63012580428881</v>
+        <v>753.83837835867121</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19952,7 +19952,7 @@
       </c>
       <c r="C49" s="218" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">Low Growth </v>
+        <v xml:space="preserve">High Growth </v>
       </c>
       <c r="E49" s="222" t="s">
         <v>253</v>
@@ -19974,7 +19974,7 @@
       </c>
       <c r="C51" s="218" t="str">
         <f>IF(C50="Y","N",IF(C46&gt;8%,"N","Y"))</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E51" s="221" t="s">
         <v>246</v>
@@ -19986,7 +19986,7 @@
       </c>
       <c r="C52" s="218" t="str">
         <f>IF(C46&gt;8%,"Y","N")</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E52" s="221"/>
     </row>
@@ -20003,7 +20003,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.1626719368258833</v>
+        <v>0.139581174029313</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20081,19 +20081,19 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>299.82734770352448</v>
+        <v>343.12060147414661</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>299.82734770352448</v>
+        <v>343.12060147414661</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.53917050691244228</v>
+        <v>0.54483386436049164</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20106,19 +20106,19 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>375.81247336701699</v>
+        <v>436.24766286961818</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>375.81247336701699</v>
+        <v>436.24766286961818</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.42238267148014419</v>
+        <v>0.42129629629629628</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20152,11 +20152,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>466.34247764114394</v>
+        <v>540.3197599894944</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>466.34247764114394</v>
+        <v>540.3197599894944</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20177,11 +20177,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>527.39872343314846</v>
+        <v>611.06153809014074</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>527.39872343314846</v>
+        <v>611.06153809014074</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.1618874917917271</v>
+        <v>0.22033584470025575</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1499999999999999</v>
+        <v>1.143294</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20403,7 +20403,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>650.62534451664794</v>
+        <v>753.83596143870022</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20419,7 +20419,7 @@
       </c>
       <c r="C19" s="352" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">Low Growth </v>
+        <v xml:space="preserve">High Growth </v>
       </c>
       <c r="D19" s="343" t="s">
         <v>362</v>
@@ -20455,14 +20455,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>299.82734770352448</v>
+        <v>343.12060147414661</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20471,14 +20471,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>375.81247336701699</v>
+        <v>436.24766286961818</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20487,7 +20487,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>466.34247764114394</v>
+        <v>540.3197599894944</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20503,7 +20503,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>527.39872343314846</v>
+        <v>611.06153809014074</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>4.3000834340575951E-2</v>
+        <v>4.2750083388325602E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-52.291661600432249</v>
+        <v>-51.986733006786601</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21010,7 +21010,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>64.673688290789485</v>
+        <v>64.296556331069468</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>93.456458250173469</v>
+        <v>92.911485198846819</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21054,7 +21054,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>105.83848494053072</v>
+        <v>105.22130852312968</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>28.203386754513204</v>
+        <v>28.038924222708193</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21213,7 +21213,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>452.3809802959654</v>
+        <v>449.74300911869176</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>1309.54 HKD</v>
+        <v>1301.9 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21291,7 +21291,7 @@
       </c>
       <c r="C119" s="401">
         <f>DCF!C91</f>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="D119" s="402">
         <f>DCF!D91</f>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>802.29 HKD</v>
+        <v>965.98 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21313,7 +21313,7 @@
       </c>
       <c r="C120" s="401">
         <f>DCF!C92</f>
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="D120" s="402">
         <f>DCF!D92</f>
@@ -21321,7 +21321,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>515.18 HKD</v>
+        <v>663.56 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21335,7 +21335,7 @@
       </c>
       <c r="C121" s="401">
         <f>DCF!C93</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D121" s="402">
         <f>DCF!D93</f>
@@ -21343,7 +21343,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>407.35 HKD</v>
+        <v>472.26 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21365,7 +21365,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>353.58 HKD</v>
+        <v>351.52 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>650.62534451664794</v>
+        <v>753.83596143870022</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21494,15 +21494,15 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>299.82734770352448</v>
+        <v>343.12060147414661</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>299.82734770352448</v>
+        <v>343.12060147414661</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21515,15 +21515,15 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>375.81247336701699</v>
+        <v>436.24766286961818</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>375.81247336701699</v>
+        <v>436.24766286961818</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21555,11 +21555,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>466.34247764114394</v>
+        <v>540.3197599894944</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>466.34247764114394</v>
+        <v>540.3197599894944</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21576,11 +21576,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>527.39872343314846</v>
+        <v>611.06153809014074</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>527.39872343314846</v>
+        <v>611.06153809014074</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/9961.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9961.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17325DF1-B222-4923-9E1E-5DFE7C4F86B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE31761-CCF2-4A7D-9A59-0A53C6C1E31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>414.8</v>
+        <v>417.2</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>285983.97033679998</v>
+        <v>287638.6509752</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.22033584470025575</v>
+        <v>0.21845382849375244</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.143294</v>
+        <v>1.1445970000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>753.83596143870022</v>
+        <v>754.69510025842169</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>343.12060147414661</v>
+        <v>343.51165237069711</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>436.24766286961818</v>
+        <v>436.74484968658663</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>540.3197599894944</v>
+        <v>540.9355566675722</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>611.06153809014074</v>
+        <v>611.75795841958484</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>4.2750083388325602E-2</v>
+        <v>4.255259922891147E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-51.986733006786601</v>
+        <v>-52.045981732930393</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>64.296556331069468</v>
+        <v>64.369834431802431</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>92.911485198846819</v>
+        <v>93.017375429368542</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>105.22130852312968</v>
+        <v>105.34122812824057</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>28.038924222708193</v>
+        <v>28.070879886135263</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>449.74300911869176</v>
+        <v>450.25557643810532</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>1301.9 HKD</v>
+        <v>1303.39 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.16651179664669991</v>
+        <v>-0.16651179664669974</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>965.98 HKD</v>
+        <v>967.08 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-7.933076973604565E-2</v>
+        <v>-7.9330769736045748E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>663.56 HKD</v>
+        <v>664.32 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>472.26 HKD</v>
+        <v>472.8 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>351.52 HKD</v>
+        <v>351.92 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.28955874359217809</v>
+        <v>0.28955874359217804</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>753.83596143870022</v>
+        <v>754.69510025842169</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>343.12060147414661</v>
+        <v>343.51165237069711</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>343.12060147414661</v>
+        <v>343.51165237069711</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>436.24766286961818</v>
+        <v>436.74484968658663</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>436.24766286961818</v>
+        <v>436.74484968658663</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>540.3197599894944</v>
+        <v>540.9355566675722</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>540.3197599894944</v>
+        <v>540.9355566675722</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>611.06153809014074</v>
+        <v>611.75795841958484</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>611.06153809014074</v>
+        <v>611.75795841958484</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -10004,11 +10004,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>283.26219326166739</v>
+        <v>283.58502416764605</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>28.038924222708193</v>
+        <v>28.070879886135263</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10414,11 +10414,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-35842.266900000002</v>
+        <v>-35883.115949999999</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-51.986733006786601</v>
+        <v>-52.045981732930393</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10431,11 +10431,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>44329.277865339827</v>
+        <v>44379.799471382139</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>64.296556331069468</v>
+        <v>64.369834431802431</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10448,11 +10448,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>64057.848184800001</v>
+        <v>64130.854232400001</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>92.911485198846819</v>
+        <v>93.017375429368542</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10465,11 +10465,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>72544.859150139819</v>
+        <v>72627.537753782148</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>105.22130852312969</v>
+        <v>105.34122812824057</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15217,18 +15217,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>17.73273458947746</v>
+        <v>17.752944398301864</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>15.666064562038839</v>
+        <v>15.68391900903527</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>16.690369114112084</v>
+        <v>16.709390950101504</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15274,18 +15274,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.2750083388325602E-2</v>
+        <v>4.255259922891147E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.7767754489003949E-2</v>
+        <v>3.7593286215329029E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>4.0237148298245137E-2</v>
+        <v>4.0051272651250011E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15331,11 +15331,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11641911244462423</v>
+        <v>0.11574939559451133</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9678170003376038E-2</v>
+        <v>5.9334863176894487E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>105.22130852312968</v>
+        <v>105.34122812824057</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.143294</v>
+        <v>1.1445970000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>310075.43726852245</v>
+        <v>310428.82694323506</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>449.74300911869176</v>
+        <v>450.25557643810532</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16451,7 +16451,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>753.83837835867121</v>
+        <v>754.69751993293062</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18639,23 +18639,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>449.74300911869176</v>
+        <v>450.25557643810532</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>449.74300911869176</v>
+        <v>450.25557643810532</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>449.74300911869176</v>
+        <v>450.25557643810532</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>449.74300911869176</v>
+        <v>450.25557643810532</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>449.74300911869176</v>
+        <v>450.25557643810532</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18670,23 +18670,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>354.37185962357654</v>
+        <v>354.77573345925623</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>364.33788166759444</v>
+        <v>364.75311367249691</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>374.30390371161235</v>
+        <v>374.73049388573747</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>384.2699257556302</v>
+        <v>384.7078740989781</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>391.74444228864354</v>
+        <v>392.19090925890856</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18701,23 +18701,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>354.06353294263965</v>
+        <v>354.46705538168356</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>373.68124329543735</v>
+        <v>374.1071238301152</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>394.04233990792875</v>
+        <v>394.49142576764643</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>415.14682278011378</v>
+        <v>415.61996119427715</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>431.46303216717632</v>
+        <v>431.95476599147156</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18732,23 +18732,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>353.7760488578499</v>
+        <v>354.17924365434305</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>382.74147275273947</v>
+        <v>383.17767913447233</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>413.91880712659685</v>
+        <v>414.39054598439373</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>447.39122806442299</v>
+        <v>447.90111508400673</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>474.0517299390296</v>
+        <v>474.59200164876535</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18763,23 +18763,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>353.50799842914148</v>
+        <v>353.91088773141473</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>391.52714980224459</v>
+        <v>391.97336912657619</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>433.9342706195215</v>
+        <v>434.42882088797148</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>481.0637072424426</v>
+        <v>481.61197042805975</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>519.71793267807971</v>
+        <v>520.31024967290307</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18794,23 +18794,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>353.25806795948324</v>
+        <v>353.66067241866102</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>400.04659421388601</v>
+        <v>400.50252305831333</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>454.08970238862054</v>
+        <v>454.60722358807789</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>516.22750834209978</v>
+        <v>516.8158473374674</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>568.68402419314532</v>
+        <v>569.33214732116278</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18825,23 +18825,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>353.02503255653852</v>
+        <v>353.42737142774854</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>408.30787364335629</v>
+        <v>408.77321777999771</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>474.38608123302777</v>
+        <v>474.92673399937365</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>552.9486805860306</v>
+        <v>553.57887031046164</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>621.18845798552297</v>
+        <v>621.89641985775813</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18857,23 +18857,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>352.80775012955058</v>
+        <v>353.20984136629181</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>416.31881127193367</v>
+        <v>416.79328538890388</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>494.82439279662685</v>
+        <v>495.38833888907027</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>591.29619845381865</v>
+        <v>591.97009243610603</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>677.48691846219867</v>
+        <v>678.25904309047132</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18888,23 +18888,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>352.60515579203252</v>
+        <v>353.00701613416413</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>424.08699321479656</v>
+        <v>424.57032064602498</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>515.40562961591536</v>
+        <v>515.99303192484865</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>631.34209123882806</v>
+        <v>632.06162509878379</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>737.85356605956633</v>
+        <v>738.69448991342688</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18920,23 +18920,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>352.41625664283151</v>
+        <v>352.81790169861387</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>431.61977570484538</v>
+        <v>432.1116881680818</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>536.13079116820586</v>
+        <v>536.741813723115</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>673.16157834298701</v>
+        <v>673.92877342717441</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>802.58237234112619</v>
+        <v>803.49706692638654</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18952,23 +18952,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>352.24012689998693</v>
+        <v>352.64157122257649</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>438.92429205883207</v>
+        <v>439.42452940159143</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>557.00088392016266</v>
+        <v>557.63569189759289</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>716.83321056364719</v>
+        <v>717.65017774213709</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>871.9885515707706</v>
+        <v>872.98234763958294</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18984,23 +18984,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>351.52276859915486</v>
+        <v>351.92339535612615</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>472.25777790512984</v>
+        <v>472.79600506683136</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>663.5610374500701</v>
+        <v>664.3172909000117</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>965.97517402652591</v>
+        <v>967.07608564834561</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>1301.9025540362777</v>
+        <v>1303.3863185167256</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19016,23 +19016,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>351.01723546737679</v>
+        <v>351.41728607361983</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>500.83769236140097</v>
+        <v>501.40849174733927</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>773.89954635968877</v>
+        <v>774.78155143354263</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>1275.3966773574077</v>
+        <v>1276.8502333723932</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1911.2770698535005</v>
+        <v>1913.4553319820689</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19048,23 +19048,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>350.66097870276019</v>
+        <v>351.0606232869614</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>525.34192555483708</v>
+        <v>525.94065215446767</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>888.15038164007353</v>
+        <v>889.16259717455296</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1659.6822685633556</v>
+        <v>1661.573790775436</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>2775.0249319791769</v>
+        <v>2778.1875983505297</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19080,23 +19080,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>350.40991922840152</v>
+        <v>350.80927768279258</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>546.35169608151352</v>
+        <v>546.97436729293793</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>1006.4522645571062</v>
+        <v>1007.5993074880741</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2136.9452060735093</v>
+        <v>2139.3806597744065</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>3999.3301005767626</v>
+        <v>4003.8880945144997</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>1301.9025540362777</v>
+        <v>1303.3863185167256</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>965.97517402652591</v>
+        <v>967.07608564834561</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>663.5610374500701</v>
+        <v>664.3172909000117</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>472.25777790512984</v>
+        <v>472.79600506683136</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>351.52276859915486</v>
+        <v>351.92339535612615</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>965.97517402652591</v>
+        <v>967.07608564834561</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19639,7 +19639,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>663.5610374500701</v>
+        <v>664.3172909000117</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19662,7 +19662,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>472.25777790512984</v>
+        <v>472.79600506683136</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>676.21804987912617</v>
+        <v>676.98872839138335</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>1301.9025540362777</v>
+        <v>1303.3863185167256</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>351.52276859915486</v>
+        <v>351.92339535612615</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19793,7 +19793,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>414.8</v>
+        <v>417.2</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19804,7 +19804,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22033584470025575</v>
+        <v>0.21845382849375244</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19813,7 +19813,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>449.74300911869176</v>
+        <v>450.25557643810532</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.18787518536183473</v>
+        <v>0.18787518536183476</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>753.83596143870022</v>
+        <v>754.69510025842169</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19936,7 +19936,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>753.83837835867121</v>
+        <v>754.69751993293062</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20081,11 +20081,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>343.12060147414661</v>
+        <v>343.51165237069711</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>343.12060147414661</v>
+        <v>343.51165237069711</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20093,7 +20093,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.54483386436049164</v>
+        <v>0.54483386436049175</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20106,11 +20106,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>436.24766286961818</v>
+        <v>436.74484968658663</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>436.24766286961818</v>
+        <v>436.74484968658663</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20152,11 +20152,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>540.3197599894944</v>
+        <v>540.9355566675722</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>540.3197599894944</v>
+        <v>540.9355566675722</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20177,11 +20177,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>611.06153809014074</v>
+        <v>611.75795841958484</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>611.06153809014074</v>
+        <v>611.75795841958484</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>414.8</v>
+        <v>417.2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20318,14 +20318,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>285983.97033679998</v>
+        <v>287638.6509752</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.22033584470025575</v>
+        <v>0.21845382849375244</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.143294</v>
+        <v>1.1445970000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20403,7 +20403,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>753.83596143870022</v>
+        <v>754.69510025842169</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20455,7 +20455,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>343.12060147414661</v>
+        <v>343.51165237069711</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20471,7 +20471,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>436.24766286961818</v>
+        <v>436.74484968658663</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>540.3197599894944</v>
+        <v>540.9355566675722</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20503,7 +20503,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>611.06153809014074</v>
+        <v>611.75795841958484</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>4.2750083388325602E-2</v>
+        <v>4.255259922891147E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-51.986733006786601</v>
+        <v>-52.045981732930393</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21010,7 +21010,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>64.296556331069468</v>
+        <v>64.369834431802431</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>92.911485198846819</v>
+        <v>93.017375429368542</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21054,7 +21054,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>105.22130852312968</v>
+        <v>105.34122812824057</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>28.038924222708193</v>
+        <v>28.070879886135263</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21213,7 +21213,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>449.74300911869176</v>
+        <v>450.25557643810532</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>1301.9 HKD</v>
+        <v>1303.39 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>965.98 HKD</v>
+        <v>967.08 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21321,7 +21321,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>663.56 HKD</v>
+        <v>664.32 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21343,7 +21343,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>472.26 HKD</v>
+        <v>472.8 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21365,7 +21365,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>351.52 HKD</v>
+        <v>351.92 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>753.83596143870022</v>
+        <v>754.69510025842169</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21494,11 +21494,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>343.12060147414661</v>
+        <v>343.51165237069711</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>343.12060147414661</v>
+        <v>343.51165237069711</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21515,11 +21515,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>436.24766286961818</v>
+        <v>436.74484968658663</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>436.24766286961818</v>
+        <v>436.74484968658663</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21555,11 +21555,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>540.3197599894944</v>
+        <v>540.9355566675722</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>540.3197599894944</v>
+        <v>540.9355566675722</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21576,11 +21576,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>611.06153809014074</v>
+        <v>611.75795841958484</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>611.06153809014074</v>
+        <v>611.75795841958484</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
